--- a/template_etf_output.xlsx
+++ b/template_etf_output.xlsx
@@ -472,7 +472,11 @@
           <t>AGG</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>iShares Core US Aggregate Bond</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -494,7 +498,11 @@
           <t>BND</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Vanguard Total Bond Market</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -516,7 +524,11 @@
           <t>DBC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PowerShares DB Commodity Tracking</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>COMMODITY</t>
@@ -538,14 +550,18 @@
           <t>GSG</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>iShares S&amp;P GSCI Commodity-Indexed Trust</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>COMMODITY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0711</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -560,14 +576,18 @@
           <t>JNK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SPDR Barclays High YIeld Bond</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2688</v>
+        <v>0.15</v>
       </c>
       <c r="E6" t="n">
         <v>0.08309999999999999</v>
@@ -582,14 +602,18 @@
           <t>SPY</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SP 500</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="n">
         <v>0.1963</v>
@@ -604,7 +628,11 @@
           <t>TIP</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>iShares TIPS Bond</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -626,14 +654,18 @@
           <t>VBR</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vanguard Small-Cap Value</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
         <v>0.1348</v>
@@ -648,14 +680,18 @@
           <t>VNQ</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vanguard U.S. Real Estate REIT</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>REALESTATE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1573</v>
+        <v>0.1289</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -670,14 +706,18 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vanguard Total U.S. Stock</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E11" t="n">
         <v>0.1927</v>
@@ -692,14 +732,18 @@
           <t>VTV</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vanguard Value ETF</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E12" t="n">
         <v>0.1656</v>
@@ -714,14 +758,18 @@
           <t>VWO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE Emerging Markets</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
@@ -787,7 +835,11 @@
           <t>AGG</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>iShares Core US Aggregate Bond</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -812,7 +864,11 @@
           <t>BND</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Vanguard Total Bond Market</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -837,14 +893,18 @@
           <t>DBC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PowerShares DB Commodity Tracking</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>COMMODITY</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
       <c r="E4" t="n">
         <v>0.0636</v>
@@ -862,14 +922,18 @@
           <t>GSG</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>iShares S&amp;P GSCI Commodity-Indexed Trust</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>COMMODITY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1068</v>
+        <v>0.15</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -887,14 +951,18 @@
           <t>JNK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SPDR Barclays High YIeld Bond</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="E6" t="n">
         <v>0.08309999999999999</v>
@@ -912,14 +980,18 @@
           <t>SPY</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SP 500</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1406</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="n">
         <v>0.1963</v>
@@ -937,14 +1009,18 @@
           <t>TIP</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>iShares TIPS Bond</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E8" t="n">
         <v>0.0434</v>
@@ -962,7 +1038,11 @@
           <t>VBR</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vanguard Small-Cap Value</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>STOCK</t>
@@ -987,14 +1067,18 @@
           <t>VNQ</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vanguard U.S. Real Estate REIT</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>REALESTATE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.0469</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -1012,14 +1096,18 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vanguard Total U.S. Stock</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E11" t="n">
         <v>0.1927</v>
@@ -1037,14 +1125,18 @@
           <t>VTV</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vanguard Value ETF</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2526</v>
+        <v>0.15</v>
       </c>
       <c r="E12" t="n">
         <v>0.1656</v>
@@ -1062,14 +1154,18 @@
           <t>VWO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE Emerging Markets</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
@@ -1133,7 +1229,11 @@
           <t>AGG</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>iShares Core US Aggregate Bond</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -1155,7 +1255,11 @@
           <t>BND</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Vanguard Total Bond Market</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -1177,7 +1281,11 @@
           <t>DBC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PowerShares DB Commodity Tracking</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>COMMODITY</t>
@@ -1199,7 +1307,11 @@
           <t>GSG</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>iShares S&amp;P GSCI Commodity-Indexed Trust</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>COMMODITY</t>
@@ -1221,14 +1333,18 @@
           <t>JNK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SPDR Barclays High YIeld Bond</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
         <v>0.08309999999999999</v>
@@ -1243,14 +1359,18 @@
           <t>SPY</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SP 500</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="n">
         <v>0.1963</v>
@@ -1265,7 +1385,11 @@
           <t>TIP</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>iShares TIPS Bond</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -1287,14 +1411,18 @@
           <t>VBR</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vanguard Small-Cap Value</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E9" t="n">
         <v>0.1348</v>
@@ -1309,14 +1437,18 @@
           <t>VNQ</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vanguard U.S. Real Estate REIT</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>REALESTATE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -1331,14 +1463,18 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vanguard Total U.S. Stock</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E11" t="n">
         <v>0.1927</v>
@@ -1353,14 +1489,18 @@
           <t>VTV</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vanguard Value ETF</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E12" t="n">
         <v>0.1656</v>
@@ -1375,14 +1515,18 @@
           <t>VWO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE Emerging Markets</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
@@ -1443,14 +1587,18 @@
           <t>AGG</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>iShares Core US Aggregate Bond</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.0655</v>
       </c>
       <c r="E2" t="n">
         <v>0.0355</v>
@@ -1465,14 +1613,18 @@
           <t>BND</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Vanguard Total Bond Market</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2326</v>
+        <v>0.15</v>
       </c>
       <c r="E3" t="n">
         <v>0.0336</v>
@@ -1487,14 +1639,18 @@
           <t>DBC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PowerShares DB Commodity Tracking</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>COMMODITY</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2015</v>
+        <v>0.15</v>
       </c>
       <c r="E4" t="n">
         <v>0.0636</v>
@@ -1509,14 +1665,18 @@
           <t>GSG</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>iShares S&amp;P GSCI Commodity-Indexed Trust</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>COMMODITY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -1531,7 +1691,11 @@
           <t>JNK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SPDR Barclays High YIeld Bond</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -1553,14 +1717,18 @@
           <t>SPY</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SP 500</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0128</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="n">
         <v>0.1963</v>
@@ -1575,14 +1743,18 @@
           <t>TIP</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>iShares TIPS Bond</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2674</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>0.0434</v>
@@ -1597,7 +1769,11 @@
           <t>VBR</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vanguard Small-Cap Value</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>STOCK</t>
@@ -1619,7 +1795,11 @@
           <t>VNQ</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vanguard U.S. Real Estate REIT</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>REALESTATE</t>
@@ -1641,14 +1821,18 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vanguard Total U.S. Stock</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.1125</v>
       </c>
       <c r="E11" t="n">
         <v>0.1927</v>
@@ -1663,14 +1847,18 @@
           <t>VTV</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vanguard Value ETF</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2857</v>
+        <v>0.15</v>
       </c>
       <c r="E12" t="n">
         <v>0.1656</v>
@@ -1685,14 +1873,18 @@
           <t>VWO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE Emerging Markets</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
@@ -1758,14 +1950,18 @@
           <t>AGG</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>iShares Core US Aggregate Bond</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1311</v>
+        <v>0.1007</v>
       </c>
       <c r="E2" t="n">
         <v>0.0355</v>
@@ -1774,7 +1970,7 @@
         <v>0.0514</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0038</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="3">
@@ -1783,14 +1979,18 @@
           <t>BND</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Vanguard Total Bond Market</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1334</v>
+        <v>0.1029</v>
       </c>
       <c r="E3" t="n">
         <v>0.0336</v>
@@ -1799,7 +1999,7 @@
         <v>0.0504</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0038</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="4">
@@ -1808,14 +2008,18 @@
           <t>DBC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PowerShares DB Commodity Tracking</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>COMMODITY</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0803</v>
+        <v>0.0675</v>
       </c>
       <c r="E4" t="n">
         <v>0.0636</v>
@@ -1824,7 +2028,7 @@
         <v>0.1398</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005</v>
+        <v>0.0034</v>
       </c>
     </row>
     <row r="5">
@@ -1833,14 +2037,18 @@
           <t>GSG</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>iShares S&amp;P GSCI Commodity-Indexed Trust</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>COMMODITY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0557</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -1849,7 +2057,7 @@
         <v>0.1525</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0048</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="6">
@@ -1858,14 +2066,18 @@
           <t>JNK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SPDR Barclays High YIeld Bond</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.0882</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0.08309999999999999</v>
@@ -1874,7 +2086,7 @@
         <v>0.042</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1883,14 +2095,18 @@
           <t>SPY</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SP 500</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0576</v>
+        <v>0.099</v>
       </c>
       <c r="E7" t="n">
         <v>0.1963</v>
@@ -1899,7 +2115,7 @@
         <v>0.1262</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0053</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="8">
@@ -1908,14 +2124,18 @@
           <t>TIP</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>iShares TIPS Bond</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1473</v>
+        <v>0.0964</v>
       </c>
       <c r="E8" t="n">
         <v>0.0434</v>
@@ -1924,7 +2144,7 @@
         <v>0.0417</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0038</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="9">
@@ -1933,14 +2153,18 @@
           <t>VBR</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vanguard Small-Cap Value</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0363</v>
+        <v>0.0471</v>
       </c>
       <c r="E9" t="n">
         <v>0.1348</v>
@@ -1949,7 +2173,7 @@
         <v>0.1584</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0043</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="10">
@@ -1958,14 +2182,18 @@
           <t>VNQ</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vanguard U.S. Real Estate REIT</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>REALESTATE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0706</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -1974,7 +2202,7 @@
         <v>0.1586</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0077</v>
+        <v>0.0083</v>
       </c>
     </row>
     <row r="11">
@@ -1983,14 +2211,18 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vanguard Total U.S. Stock</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.053</v>
+        <v>0.0837</v>
       </c>
       <c r="E11" t="n">
         <v>0.1927</v>
@@ -1999,7 +2231,7 @@
         <v>0.1291</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0051</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="12">
@@ -2008,14 +2240,18 @@
           <t>VTV</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vanguard Value ETF</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.0762</v>
+        <v>0.15</v>
       </c>
       <c r="E12" t="n">
         <v>0.1656</v>
@@ -2024,7 +2260,7 @@
         <v>0.1057</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="13">
@@ -2033,14 +2269,18 @@
           <t>VWO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE Emerging Markets</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.0506</v>
+        <v>0.1202</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
@@ -2049,7 +2289,7 @@
         <v>0.1471</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0051</v>
+        <v>0.0133</v>
       </c>
     </row>
   </sheetData>
@@ -2109,14 +2349,18 @@
           <t>AGG</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>iShares Core US Aggregate Bond</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E2" t="n">
         <v>0.0355</v>
@@ -2134,14 +2378,18 @@
           <t>BND</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Vanguard Total Bond Market</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0495</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0.0336</v>
@@ -2159,14 +2407,18 @@
           <t>DBC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PowerShares DB Commodity Tracking</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>COMMODITY</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.136</v>
+        <v>0.1121</v>
       </c>
       <c r="E4" t="n">
         <v>0.0636</v>
@@ -2184,14 +2436,18 @@
           <t>GSG</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>iShares S&amp;P GSCI Commodity-Indexed Trust</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>COMMODITY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.0325</v>
+        <v>0.0866</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2209,7 +2465,11 @@
           <t>JNK</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SPDR Barclays High YIeld Bond</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>BOND</t>
@@ -2234,14 +2494,18 @@
           <t>SPY</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SP 500</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0542</v>
+        <v>0.15</v>
       </c>
       <c r="E7" t="n">
         <v>0.1963</v>
@@ -2259,14 +2523,18 @@
           <t>TIP</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>iShares TIPS Bond</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>BOND</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4505</v>
+        <v>0.15</v>
       </c>
       <c r="E8" t="n">
         <v>0.0434</v>
@@ -2284,7 +2552,11 @@
           <t>VBR</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vanguard Small-Cap Value</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>STOCK</t>
@@ -2309,14 +2581,18 @@
           <t>VNQ</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vanguard U.S. Real Estate REIT</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>REALESTATE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -2334,14 +2610,18 @@
           <t>VTI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vanguard Total U.S. Stock</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.1461</v>
       </c>
       <c r="E11" t="n">
         <v>0.1927</v>
@@ -2359,14 +2639,18 @@
           <t>VTV</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vanguard Value ETF</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2773</v>
+        <v>0.15</v>
       </c>
       <c r="E12" t="n">
         <v>0.1656</v>
@@ -2384,14 +2668,18 @@
           <t>VWO</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE Emerging Markets</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>STOCK</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.0539</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
@@ -2446,7 +2734,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1455</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="3">
@@ -2461,7 +2749,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0926</v>
       </c>
     </row>
     <row r="4">
@@ -2491,7 +2779,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0265</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="6">
@@ -2511,7 +2799,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1195</v>
+        <v>0.1265</v>
       </c>
     </row>
     <row r="8">
@@ -2526,7 +2814,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0616</v>
+        <v>0.07340000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2541,7 +2829,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.9414</v>
+        <v>1.7237</v>
       </c>
     </row>
     <row r="10">
@@ -2571,7 +2859,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0181</v>
+        <v>0.0221</v>
       </c>
     </row>
     <row r="12">
@@ -2591,7 +2879,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1589</v>
+        <v>0.1492</v>
       </c>
     </row>
     <row r="14">
@@ -2606,7 +2894,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.121</v>
+        <v>0.1056</v>
       </c>
     </row>
     <row r="15">
@@ -2621,7 +2909,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0381</v>
+        <v>0.0337</v>
       </c>
     </row>
     <row r="16">
@@ -2641,7 +2929,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.082</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="18">
@@ -2656,7 +2944,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.052</v>
+        <v>0.0697</v>
       </c>
     </row>
     <row r="19">
@@ -2671,7 +2959,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.016</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="20">
@@ -2691,7 +2979,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0881</v>
+        <v>0.1115</v>
       </c>
     </row>
     <row r="22">
@@ -2706,7 +2994,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0577</v>
+        <v>0.0731</v>
       </c>
     </row>
     <row r="23">
@@ -2721,7 +3009,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0178</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="24">
@@ -2741,7 +3029,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.089</v>
+        <v>0.1154</v>
       </c>
     </row>
     <row r="26">
@@ -2756,7 +3044,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0524</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2771,7 +3059,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0158</v>
+        <v>0.0213</v>
       </c>
     </row>
     <row r="28">

--- a/template_etf_output.xlsx
+++ b/template_etf_output.xlsx
@@ -489,7 +489,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0514</v>
+        <v>0.0609</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0504</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="4">
@@ -541,7 +541,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1398</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="5">
@@ -567,7 +567,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1525</v>
+        <v>0.1981</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +593,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.042</v>
+        <v>0.0746</v>
       </c>
     </row>
     <row r="7">
@@ -619,7 +619,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1262</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0417</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1584</v>
+        <v>0.2128</v>
       </c>
     </row>
     <row r="10">
@@ -697,7 +697,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1586</v>
+        <v>0.2003</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1291</v>
+        <v>0.1915</v>
       </c>
     </row>
     <row r="12">
@@ -749,7 +749,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1057</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="13">
@@ -775,7 +775,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1471</v>
+        <v>0.1804</v>
       </c>
     </row>
   </sheetData>
@@ -852,7 +852,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0514</v>
+        <v>0.0609</v>
       </c>
       <c r="G2" t="n">
         <v>0.6908</v>
@@ -881,7 +881,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0504</v>
+        <v>0.0604</v>
       </c>
       <c r="G3" t="n">
         <v>0.6662</v>
@@ -910,7 +910,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1398</v>
+        <v>0.1694</v>
       </c>
       <c r="G4" t="n">
         <v>0.4547</v>
@@ -939,7 +939,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1525</v>
+        <v>0.1981</v>
       </c>
       <c r="G5" t="n">
         <v>0.5244</v>
@@ -968,7 +968,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.042</v>
+        <v>0.0746</v>
       </c>
       <c r="G6" t="n">
         <v>1.9794</v>
@@ -997,7 +997,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1262</v>
+        <v>0.1899</v>
       </c>
       <c r="G7" t="n">
         <v>1.5549</v>
@@ -1026,7 +1026,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0417</v>
+        <v>0.0586</v>
       </c>
       <c r="G8" t="n">
         <v>1.0396</v>
@@ -1055,7 +1055,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1584</v>
+        <v>0.2128</v>
       </c>
       <c r="G9" t="n">
         <v>0.8508</v>
@@ -1084,7 +1084,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1586</v>
+        <v>0.2003</v>
       </c>
       <c r="G10" t="n">
         <v>0.7662</v>
@@ -1113,7 +1113,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1291</v>
+        <v>0.1915</v>
       </c>
       <c r="G11" t="n">
         <v>1.4926</v>
@@ -1142,7 +1142,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1057</v>
+        <v>0.1548</v>
       </c>
       <c r="G12" t="n">
         <v>1.5673</v>
@@ -1171,7 +1171,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1471</v>
+        <v>0.1804</v>
       </c>
       <c r="G13" t="n">
         <v>0.8749</v>
@@ -1246,7 +1246,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0514</v>
+        <v>0.0609</v>
       </c>
     </row>
     <row r="3">
@@ -1272,7 +1272,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0504</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="4">
@@ -1298,7 +1298,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1398</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="5">
@@ -1324,7 +1324,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1525</v>
+        <v>0.1981</v>
       </c>
     </row>
     <row r="6">
@@ -1350,7 +1350,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.042</v>
+        <v>0.0746</v>
       </c>
     </row>
     <row r="7">
@@ -1376,7 +1376,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1262</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0417</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="9">
@@ -1428,7 +1428,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1584</v>
+        <v>0.2128</v>
       </c>
     </row>
     <row r="10">
@@ -1454,7 +1454,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1586</v>
+        <v>0.2003</v>
       </c>
     </row>
     <row r="11">
@@ -1480,7 +1480,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1291</v>
+        <v>0.1915</v>
       </c>
     </row>
     <row r="12">
@@ -1506,7 +1506,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1057</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="13">
@@ -1532,7 +1532,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1471</v>
+        <v>0.1804</v>
       </c>
     </row>
   </sheetData>
@@ -1604,7 +1604,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0514</v>
+        <v>0.0609</v>
       </c>
     </row>
     <row r="3">
@@ -1630,7 +1630,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0504</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="4">
@@ -1656,7 +1656,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1398</v>
+        <v>0.1694</v>
       </c>
     </row>
     <row r="5">
@@ -1682,7 +1682,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1525</v>
+        <v>0.1981</v>
       </c>
     </row>
     <row r="6">
@@ -1708,7 +1708,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.042</v>
+        <v>0.0746</v>
       </c>
     </row>
     <row r="7">
@@ -1734,7 +1734,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1262</v>
+        <v>0.1899</v>
       </c>
     </row>
     <row r="8">
@@ -1760,7 +1760,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0417</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="9">
@@ -1786,7 +1786,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1584</v>
+        <v>0.2128</v>
       </c>
     </row>
     <row r="10">
@@ -1812,7 +1812,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1586</v>
+        <v>0.2003</v>
       </c>
     </row>
     <row r="11">
@@ -1838,7 +1838,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1291</v>
+        <v>0.1915</v>
       </c>
     </row>
     <row r="12">
@@ -1864,7 +1864,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1057</v>
+        <v>0.1548</v>
       </c>
     </row>
     <row r="13">
@@ -1890,7 +1890,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1471</v>
+        <v>0.1804</v>
       </c>
     </row>
   </sheetData>
@@ -1967,7 +1967,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0514</v>
+        <v>0.0609</v>
       </c>
       <c r="G2" t="n">
         <v>0.0023</v>
@@ -1996,7 +1996,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0504</v>
+        <v>0.0604</v>
       </c>
       <c r="G3" t="n">
         <v>0.0023</v>
@@ -2025,7 +2025,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1398</v>
+        <v>0.1694</v>
       </c>
       <c r="G4" t="n">
         <v>0.0034</v>
@@ -2054,7 +2054,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1525</v>
+        <v>0.1981</v>
       </c>
       <c r="G5" t="n">
         <v>0.0028</v>
@@ -2083,7 +2083,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.042</v>
+        <v>0.0746</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1262</v>
+        <v>0.1899</v>
       </c>
       <c r="G7" t="n">
         <v>0.0103</v>
@@ -2141,7 +2141,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0417</v>
+        <v>0.0586</v>
       </c>
       <c r="G8" t="n">
         <v>0.0019</v>
@@ -2170,7 +2170,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1584</v>
+        <v>0.2128</v>
       </c>
       <c r="G9" t="n">
         <v>0.0062</v>
@@ -2199,7 +2199,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1586</v>
+        <v>0.2003</v>
       </c>
       <c r="G10" t="n">
         <v>0.0083</v>
@@ -2228,7 +2228,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1291</v>
+        <v>0.1915</v>
       </c>
       <c r="G11" t="n">
         <v>0.0092</v>
@@ -2257,7 +2257,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1057</v>
+        <v>0.1548</v>
       </c>
       <c r="G12" t="n">
         <v>0.0132</v>
@@ -2286,7 +2286,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1471</v>
+        <v>0.1804</v>
       </c>
       <c r="G13" t="n">
         <v>0.0133</v>
@@ -2366,7 +2366,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0514</v>
+        <v>0.0609</v>
       </c>
       <c r="G2" t="n">
         <v>0.0173</v>
@@ -2395,7 +2395,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0504</v>
+        <v>0.0604</v>
       </c>
       <c r="G3" t="n">
         <v>0.0173</v>
@@ -2424,7 +2424,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1398</v>
+        <v>0.1694</v>
       </c>
       <c r="G4" t="n">
         <v>0.0474</v>
@@ -2453,7 +2453,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1525</v>
+        <v>0.1981</v>
       </c>
       <c r="G5" t="n">
         <v>0.0515</v>
@@ -2482,7 +2482,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.042</v>
+        <v>0.0746</v>
       </c>
       <c r="G6" t="n">
         <v>0.0123</v>
@@ -2511,7 +2511,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1262</v>
+        <v>0.1899</v>
       </c>
       <c r="G7" t="n">
         <v>0.0389</v>
@@ -2540,7 +2540,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0417</v>
+        <v>0.0586</v>
       </c>
       <c r="G8" t="n">
         <v>0.0136</v>
@@ -2569,7 +2569,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1584</v>
+        <v>0.2128</v>
       </c>
       <c r="G9" t="n">
         <v>0.052</v>
@@ -2598,7 +2598,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1586</v>
+        <v>0.2003</v>
       </c>
       <c r="G10" t="n">
         <v>0.0529</v>
@@ -2627,7 +2627,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1291</v>
+        <v>0.1915</v>
       </c>
       <c r="G11" t="n">
         <v>0.0401</v>
@@ -2656,7 +2656,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1057</v>
+        <v>0.1548</v>
       </c>
       <c r="G12" t="n">
         <v>0.0326</v>
@@ -2685,7 +2685,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1471</v>
+        <v>0.1804</v>
       </c>
       <c r="G13" t="n">
         <v>0.0481</v>

--- a/template_etf_output.xlsx
+++ b/template_etf_output.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.0711</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.1363</v>
       </c>
       <c r="E8" t="n">
         <v>0.0434</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0.1348</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1289</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -769,13 +769,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.15</v>
+        <v>0.1137</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
         <v>0.1804</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPDR Gold Shares</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1519</v>
       </c>
     </row>
   </sheetData>
@@ -789,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,7 +872,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E2" t="n">
         <v>0.0355</v>
@@ -855,7 +881,7 @@
         <v>0.0609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6908</v>
+        <v>0.5831</v>
       </c>
     </row>
     <row r="3">
@@ -884,7 +910,7 @@
         <v>0.0604</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6662</v>
+        <v>0.5567</v>
       </c>
     </row>
     <row r="4">
@@ -904,7 +930,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0031</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0.0636</v>
@@ -913,7 +939,7 @@
         <v>0.1694</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4547</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="5">
@@ -933,7 +959,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -942,7 +968,7 @@
         <v>0.1981</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5244</v>
+        <v>0.4037</v>
       </c>
     </row>
     <row r="6">
@@ -962,7 +988,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0.08309999999999999</v>
@@ -971,7 +997,7 @@
         <v>0.0746</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9794</v>
+        <v>1.1136</v>
       </c>
     </row>
     <row r="7">
@@ -1000,7 +1026,7 @@
         <v>0.1899</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5549</v>
+        <v>1.0338</v>
       </c>
     </row>
     <row r="8">
@@ -1029,7 +1055,7 @@
         <v>0.0586</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0396</v>
+        <v>0.7401</v>
       </c>
     </row>
     <row r="9">
@@ -1058,7 +1084,7 @@
         <v>0.2128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8508</v>
+        <v>0.6334</v>
       </c>
     </row>
     <row r="10">
@@ -1078,7 +1104,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0469</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -1087,7 +1113,7 @@
         <v>0.2003</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7662</v>
+        <v>0.6064000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1116,7 +1142,7 @@
         <v>0.1915</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4926</v>
+        <v>1.0062</v>
       </c>
     </row>
     <row r="12">
@@ -1145,7 +1171,7 @@
         <v>0.1548</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5673</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="13">
@@ -1174,7 +1200,36 @@
         <v>0.1804</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8749</v>
+        <v>0.7134</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPDR Gold Shares</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.3163</v>
       </c>
     </row>
   </sheetData>
@@ -1188,7 +1243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,7 +1399,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
         <v>0.08309999999999999</v>
@@ -1448,7 +1503,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -1533,6 +1588,32 @@
       </c>
       <c r="F13" t="n">
         <v>0.1804</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPDR Gold Shares</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1519</v>
       </c>
     </row>
   </sheetData>
@@ -1546,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,7 +1679,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0655</v>
+        <v>0.0472</v>
       </c>
       <c r="E2" t="n">
         <v>0.0355</v>
@@ -1650,7 +1731,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
         <v>0.0636</v>
@@ -1676,7 +1757,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -1754,7 +1835,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1028</v>
       </c>
       <c r="E8" t="n">
         <v>0.0434</v>
@@ -1832,7 +1913,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1125</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
         <v>0.1927</v>
@@ -1884,13 +1965,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
         <v>0.1804</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPDR Gold Shares</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1519</v>
       </c>
     </row>
   </sheetData>
@@ -1904,7 +2011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1961,7 +2068,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1007</v>
+        <v>0.102</v>
       </c>
       <c r="E2" t="n">
         <v>0.0355</v>
@@ -1970,7 +2077,7 @@
         <v>0.0609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0023</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="3">
@@ -1990,7 +2097,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1029</v>
+        <v>0.1085</v>
       </c>
       <c r="E3" t="n">
         <v>0.0336</v>
@@ -1999,7 +2106,7 @@
         <v>0.0604</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0023</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="4">
@@ -2019,7 +2126,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0675</v>
+        <v>0.033</v>
       </c>
       <c r="E4" t="n">
         <v>0.0636</v>
@@ -2028,7 +2135,7 @@
         <v>0.1694</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0034</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="5">
@@ -2048,7 +2155,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.0557</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2057,7 +2164,7 @@
         <v>0.1981</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2106,7 +2213,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.099</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>0.1963</v>
@@ -2115,7 +2222,7 @@
         <v>0.1899</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0103</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="8">
@@ -2135,7 +2242,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.0964</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="E8" t="n">
         <v>0.0434</v>
@@ -2144,7 +2251,7 @@
         <v>0.0586</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0019</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="9">
@@ -2164,7 +2271,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0471</v>
+        <v>0.0566</v>
       </c>
       <c r="E9" t="n">
         <v>0.1348</v>
@@ -2173,7 +2280,7 @@
         <v>0.2128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0062</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="10">
@@ -2193,7 +2300,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -2202,7 +2309,7 @@
         <v>0.2003</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0083</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="11">
@@ -2222,7 +2329,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.0837</v>
+        <v>0.068</v>
       </c>
       <c r="E11" t="n">
         <v>0.1927</v>
@@ -2231,7 +2338,7 @@
         <v>0.1915</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0092</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="12">
@@ -2260,7 +2367,7 @@
         <v>0.1548</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0132</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="13">
@@ -2280,7 +2387,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1202</v>
+        <v>0.15</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
@@ -2289,7 +2396,36 @@
         <v>0.1804</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0133</v>
+        <v>0.0225</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPDR Gold Shares</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0118</v>
       </c>
     </row>
   </sheetData>
@@ -2303,7 +2439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2360,7 +2496,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.15</v>
+        <v>0.0004</v>
       </c>
       <c r="E2" t="n">
         <v>0.0355</v>
@@ -2369,7 +2505,7 @@
         <v>0.0609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0173</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="3">
@@ -2389,7 +2525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E3" t="n">
         <v>0.0336</v>
@@ -2398,7 +2534,7 @@
         <v>0.0604</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0173</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="4">
@@ -2418,7 +2554,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1121</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
         <v>0.0636</v>
@@ -2427,7 +2563,7 @@
         <v>0.1694</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0474</v>
+        <v>0.0622</v>
       </c>
     </row>
     <row r="5">
@@ -2447,7 +2583,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.0866</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2456,7 +2592,7 @@
         <v>0.1981</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0515</v>
+        <v>0.0699</v>
       </c>
     </row>
     <row r="6">
@@ -2485,7 +2621,7 @@
         <v>0.0746</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0123</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="7">
@@ -2514,7 +2650,7 @@
         <v>0.1899</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0389</v>
+        <v>0.0615</v>
       </c>
     </row>
     <row r="8">
@@ -2534,7 +2670,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.15</v>
+        <v>0.1496</v>
       </c>
       <c r="E8" t="n">
         <v>0.0434</v>
@@ -2543,7 +2679,7 @@
         <v>0.0586</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0136</v>
+        <v>0.0194</v>
       </c>
     </row>
     <row r="9">
@@ -2572,7 +2708,7 @@
         <v>0.2128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.052</v>
+        <v>0.0721</v>
       </c>
     </row>
     <row r="10">
@@ -2592,7 +2728,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0013</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0.1215</v>
@@ -2601,7 +2737,7 @@
         <v>0.2003</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0529</v>
+        <v>0.0672</v>
       </c>
     </row>
     <row r="11">
@@ -2621,7 +2757,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1461</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
         <v>0.1927</v>
@@ -2630,7 +2766,7 @@
         <v>0.1915</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0401</v>
+        <v>0.0619</v>
       </c>
     </row>
     <row r="12">
@@ -2659,7 +2795,7 @@
         <v>0.1548</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0326</v>
+        <v>0.0513</v>
       </c>
     </row>
     <row r="13">
@@ -2679,7 +2815,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.0539</v>
+        <v>0.15</v>
       </c>
       <c r="E13" t="n">
         <v>0.1287</v>
@@ -2688,7 +2824,36 @@
         <v>0.1804</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0481</v>
+        <v>0.0599</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPDR Gold Shares</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COMMODITY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0478</v>
       </c>
     </row>
   </sheetData>
@@ -2734,7 +2899,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.143</v>
+        <v>0.1462</v>
       </c>
     </row>
     <row r="3">
@@ -2749,7 +2914,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0926</v>
+        <v>0.1132</v>
       </c>
     </row>
     <row r="4">
@@ -2779,7 +2944,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0286</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="6">
@@ -2799,7 +2964,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1265</v>
+        <v>0.1355</v>
       </c>
     </row>
     <row r="8">
@@ -2814,7 +2979,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1029</v>
       </c>
     </row>
     <row r="9">
@@ -2829,7 +2994,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.7237</v>
+        <v>1.3163</v>
       </c>
     </row>
     <row r="10">
@@ -2859,7 +3024,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0221</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="12">
@@ -2879,7 +3044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1492</v>
+        <v>0.1629</v>
       </c>
     </row>
     <row r="14">
@@ -2894,7 +3059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1056</v>
+        <v>0.1462</v>
       </c>
     </row>
     <row r="15">
@@ -2909,7 +3074,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0337</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="16">
@@ -2929,7 +3094,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.1118</v>
+        <v>0.1276</v>
       </c>
     </row>
     <row r="18">
@@ -2944,7 +3109,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0697</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="19">
@@ -2959,7 +3124,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0214</v>
+        <v>0.0313</v>
       </c>
     </row>
     <row r="20">
@@ -2979,7 +3144,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1115</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="22">
@@ -2994,7 +3159,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0731</v>
+        <v>0.1012</v>
       </c>
     </row>
     <row r="23">
@@ -3009,7 +3174,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0226</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="24">
@@ -3029,7 +3194,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1154</v>
+        <v>0.1279</v>
       </c>
     </row>
     <row r="26">
@@ -3044,7 +3209,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="27">
@@ -3059,7 +3224,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0213</v>
+        <v>0.0313</v>
       </c>
     </row>
     <row r="28">

--- a/template_etf_output.xlsx
+++ b/template_etf_output.xlsx
@@ -489,7 +489,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0609</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0604</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="4">
@@ -541,7 +541,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1694</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="5">
@@ -567,7 +567,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1981</v>
+        <v>0.1972</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +593,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0746</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="7">
@@ -619,7 +619,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1899</v>
+        <v>0.1896</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0586</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2128</v>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="10">
@@ -697,7 +697,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2003</v>
+        <v>0.1979</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1915</v>
+        <v>0.1913</v>
       </c>
     </row>
     <row r="12">
@@ -749,7 +749,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1548</v>
+        <v>0.1542</v>
       </c>
     </row>
     <row r="13">
@@ -775,7 +775,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1804</v>
+        <v>0.1799</v>
       </c>
     </row>
     <row r="14">
@@ -801,7 +801,7 @@
         <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1519</v>
+        <v>0.1583</v>
       </c>
     </row>
   </sheetData>
@@ -878,7 +878,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0609</v>
+        <v>0.0606</v>
       </c>
       <c r="G2" t="n">
         <v>0.5831</v>
@@ -907,7 +907,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0604</v>
+        <v>0.06</v>
       </c>
       <c r="G3" t="n">
         <v>0.5567</v>
@@ -936,7 +936,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1694</v>
+        <v>0.169</v>
       </c>
       <c r="G4" t="n">
         <v>0.3753</v>
@@ -965,7 +965,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1981</v>
+        <v>0.1972</v>
       </c>
       <c r="G5" t="n">
         <v>0.4037</v>
@@ -994,7 +994,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0746</v>
+        <v>0.074</v>
       </c>
       <c r="G6" t="n">
         <v>1.1136</v>
@@ -1023,7 +1023,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1899</v>
+        <v>0.1896</v>
       </c>
       <c r="G7" t="n">
         <v>1.0338</v>
@@ -1052,7 +1052,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0586</v>
+        <v>0.0583</v>
       </c>
       <c r="G8" t="n">
         <v>0.7401</v>
@@ -1081,7 +1081,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2128</v>
+        <v>0.2121</v>
       </c>
       <c r="G9" t="n">
         <v>0.6334</v>
@@ -1110,7 +1110,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2003</v>
+        <v>0.1979</v>
       </c>
       <c r="G10" t="n">
         <v>0.6064000000000001</v>
@@ -1139,7 +1139,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1915</v>
+        <v>0.1913</v>
       </c>
       <c r="G11" t="n">
         <v>1.0062</v>
@@ -1168,7 +1168,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1548</v>
+        <v>0.1542</v>
       </c>
       <c r="G12" t="n">
         <v>1.07</v>
@@ -1197,7 +1197,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1804</v>
+        <v>0.1799</v>
       </c>
       <c r="G13" t="n">
         <v>0.7134</v>
@@ -1226,7 +1226,7 @@
         <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1519</v>
+        <v>0.1583</v>
       </c>
       <c r="G14" t="n">
         <v>1.3163</v>
@@ -1301,7 +1301,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0609</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="3">
@@ -1327,7 +1327,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0604</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="4">
@@ -1353,7 +1353,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1694</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="5">
@@ -1379,7 +1379,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1981</v>
+        <v>0.1972</v>
       </c>
     </row>
     <row r="6">
@@ -1405,7 +1405,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0746</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="7">
@@ -1431,7 +1431,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1899</v>
+        <v>0.1896</v>
       </c>
     </row>
     <row r="8">
@@ -1457,7 +1457,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0586</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="9">
@@ -1483,7 +1483,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2128</v>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="10">
@@ -1509,7 +1509,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2003</v>
+        <v>0.1979</v>
       </c>
     </row>
     <row r="11">
@@ -1535,7 +1535,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1915</v>
+        <v>0.1913</v>
       </c>
     </row>
     <row r="12">
@@ -1561,7 +1561,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1548</v>
+        <v>0.1542</v>
       </c>
     </row>
     <row r="13">
@@ -1587,7 +1587,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1804</v>
+        <v>0.1799</v>
       </c>
     </row>
     <row r="14">
@@ -1613,7 +1613,7 @@
         <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1519</v>
+        <v>0.1583</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1685,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0609</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="3">
@@ -1711,7 +1711,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0604</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="4">
@@ -1737,7 +1737,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1694</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="5">
@@ -1763,7 +1763,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1981</v>
+        <v>0.1972</v>
       </c>
     </row>
     <row r="6">
@@ -1789,7 +1789,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0746</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="7">
@@ -1815,7 +1815,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1899</v>
+        <v>0.1896</v>
       </c>
     </row>
     <row r="8">
@@ -1841,7 +1841,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0586</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="9">
@@ -1867,7 +1867,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2128</v>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="10">
@@ -1893,7 +1893,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2003</v>
+        <v>0.1979</v>
       </c>
     </row>
     <row r="11">
@@ -1919,7 +1919,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1915</v>
+        <v>0.1913</v>
       </c>
     </row>
     <row r="12">
@@ -1945,7 +1945,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1548</v>
+        <v>0.1542</v>
       </c>
     </row>
     <row r="13">
@@ -1971,7 +1971,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1804</v>
+        <v>0.1799</v>
       </c>
     </row>
     <row r="14">
@@ -1997,7 +1997,7 @@
         <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1519</v>
+        <v>0.1583</v>
       </c>
     </row>
   </sheetData>
@@ -2074,7 +2074,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0609</v>
+        <v>0.0606</v>
       </c>
       <c r="G2" t="n">
         <v>0.0025</v>
@@ -2103,7 +2103,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0604</v>
+        <v>0.06</v>
       </c>
       <c r="G3" t="n">
         <v>0.0026</v>
@@ -2132,7 +2132,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1694</v>
+        <v>0.169</v>
       </c>
       <c r="G4" t="n">
         <v>0.0027</v>
@@ -2161,7 +2161,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1981</v>
+        <v>0.1972</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2190,7 +2190,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0746</v>
+        <v>0.074</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1899</v>
+        <v>0.1896</v>
       </c>
       <c r="G7" t="n">
         <v>0.0125</v>
@@ -2248,7 +2248,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0586</v>
+        <v>0.0583</v>
       </c>
       <c r="G8" t="n">
         <v>0.0021</v>
@@ -2277,7 +2277,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2128</v>
+        <v>0.2121</v>
       </c>
       <c r="G9" t="n">
         <v>0.0102</v>
@@ -2306,7 +2306,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2003</v>
+        <v>0.1979</v>
       </c>
       <c r="G10" t="n">
         <v>0.0026</v>
@@ -2335,7 +2335,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1915</v>
+        <v>0.1913</v>
       </c>
       <c r="G11" t="n">
         <v>0.0115</v>
@@ -2364,7 +2364,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1548</v>
+        <v>0.1542</v>
       </c>
       <c r="G12" t="n">
         <v>0.0201</v>
@@ -2393,7 +2393,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1804</v>
+        <v>0.1799</v>
       </c>
       <c r="G13" t="n">
         <v>0.0225</v>
@@ -2422,7 +2422,7 @@
         <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1519</v>
+        <v>0.1583</v>
       </c>
       <c r="G14" t="n">
         <v>0.0118</v>
@@ -2502,7 +2502,7 @@
         <v>0.0355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0609</v>
+        <v>0.0606</v>
       </c>
       <c r="G2" t="n">
         <v>0.0205</v>
@@ -2531,7 +2531,7 @@
         <v>0.0336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0604</v>
+        <v>0.06</v>
       </c>
       <c r="G3" t="n">
         <v>0.0203</v>
@@ -2560,7 +2560,7 @@
         <v>0.0636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1694</v>
+        <v>0.169</v>
       </c>
       <c r="G4" t="n">
         <v>0.0622</v>
@@ -2589,7 +2589,7 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1981</v>
+        <v>0.1972</v>
       </c>
       <c r="G5" t="n">
         <v>0.0699</v>
@@ -2618,7 +2618,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0746</v>
+        <v>0.074</v>
       </c>
       <c r="G6" t="n">
         <v>0.024</v>
@@ -2647,7 +2647,7 @@
         <v>0.1963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1899</v>
+        <v>0.1896</v>
       </c>
       <c r="G7" t="n">
         <v>0.0615</v>
@@ -2676,7 +2676,7 @@
         <v>0.0434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0586</v>
+        <v>0.0583</v>
       </c>
       <c r="G8" t="n">
         <v>0.0194</v>
@@ -2705,7 +2705,7 @@
         <v>0.1348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2128</v>
+        <v>0.2121</v>
       </c>
       <c r="G9" t="n">
         <v>0.0721</v>
@@ -2734,7 +2734,7 @@
         <v>0.1215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2003</v>
+        <v>0.1979</v>
       </c>
       <c r="G10" t="n">
         <v>0.0672</v>
@@ -2763,7 +2763,7 @@
         <v>0.1927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1915</v>
+        <v>0.1913</v>
       </c>
       <c r="G11" t="n">
         <v>0.0619</v>
@@ -2792,7 +2792,7 @@
         <v>0.1656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1548</v>
+        <v>0.1542</v>
       </c>
       <c r="G12" t="n">
         <v>0.0513</v>
@@ -2821,7 +2821,7 @@
         <v>0.1287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1804</v>
+        <v>0.1799</v>
       </c>
       <c r="G13" t="n">
         <v>0.0599</v>
@@ -2850,7 +2850,7 @@
         <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1519</v>
+        <v>0.1583</v>
       </c>
       <c r="G14" t="n">
         <v>0.0478</v>
